--- a/data/trans_dic/P1805_2016_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1805_2016_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,0</t>
+          <t>1,15; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,7</t>
+          <t>2,25; 6,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,72</t>
+          <t>2,72; 6,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,57</t>
+          <t>3,83; 7,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,65</t>
+          <t>2,14; 4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,61</t>
+          <t>3,51; 6,36</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,81</t>
+          <t>0,8; 4,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,67</t>
+          <t>1,98; 5,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,66</t>
+          <t>0,94; 4,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,41</t>
+          <t>4,23; 8,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,39</t>
+          <t>1,17; 3,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,13</t>
+          <t>3,37; 6,0</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,0</t>
+          <t>1,35; 4,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,19</t>
+          <t>1,41; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,39</t>
+          <t>3,3; 12,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,17</t>
+          <t>2,13; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,13</t>
+          <t>2,19; 5,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,09</t>
+          <t>2,04; 4,7</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,11</t>
+          <t>0,65; 2,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,42</t>
+          <t>2,06; 4,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,72</t>
+          <t>2,89; 5,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,76</t>
+          <t>3,38; 5,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,2</t>
+          <t>1,8; 3,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,15</t>
+          <t>2,8; 4,53</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,04</t>
+          <t>0,83; 3,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,17</t>
+          <t>0,89; 3,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,49</t>
+          <t>2,56; 5,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,43</t>
+          <t>2,36; 4,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,93</t>
+          <t>1,95; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,74</t>
+          <t>1,99; 3,71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,85</t>
+          <t>0,99; 4,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 12,28</t>
+          <t>2,24; 12,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,11; 4,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,17</t>
+          <t>1,95; 4,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,9</t>
+          <t>2,12; 4,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,53</t>
+          <t>2,38; 5,54</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,33</t>
+          <t>1,36; 2,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,95</t>
+          <t>2,57; 4,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,5</t>
+          <t>3,01; 4,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,57</t>
+          <t>3,57; 4,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,23</t>
+          <t>2,39; 3,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,05</t>
+          <t>3,31; 4,22</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>48601</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4762; 17158</t>
+          <t>4952; 18090</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13767; 38907</t>
+          <t>12385; 36206</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8521; 23313</t>
+          <t>9443; 24132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16494; 33880</t>
+          <t>18686; 36802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15916; 36098</t>
+          <t>16639; 35548</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33664; 62937</t>
+          <t>36500; 66038</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>41942</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2935; 14374</t>
+          <t>3024; 15186</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10151; 25635</t>
+          <t>9567; 26781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3438; 17357</t>
+          <t>3486; 16321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15597; 32170</t>
+          <t>17881; 35318</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8682; 25414</t>
+          <t>8756; 25563</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29123; 51174</t>
+          <t>30551; 54382</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20865</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6708; 20867</t>
+          <t>7030; 22275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3571; 27990</t>
+          <t>6652; 23192</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5402; 20578</t>
+          <t>5484; 20281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3767; 11961</t>
+          <t>3990; 13188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15185; 35313</t>
+          <t>15070; 34915</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7847; 34175</t>
+          <t>13416; 30952</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64494</t>
+          <t>73013</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7741; 24301</t>
+          <t>7484; 24147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20738; 45721</t>
+          <t>23294; 49326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23735; 47218</t>
+          <t>23902; 49171</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14869; 46509</t>
+          <t>29125; 48781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34847; 63268</t>
+          <t>35543; 63351</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44498; 83475</t>
+          <t>55823; 90305</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>37984</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4969; 18893</t>
+          <t>5169; 19152</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5519; 19798</t>
+          <t>5036; 20478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18207; 40560</t>
+          <t>18880; 41485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17939; 37281</t>
+          <t>19569; 36704</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27523; 53423</t>
+          <t>26459; 53135</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26107; 49190</t>
+          <t>27862; 51840</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24282</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>40206</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2881; 13919</t>
+          <t>2857; 12703</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5364; 29535</t>
+          <t>5324; 30565</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23072; 46303</t>
+          <t>22811; 47143</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15188; 39334</t>
+          <t>16431; 39437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28670; 53401</t>
+          <t>28992; 55522</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24761; 55321</t>
+          <t>25743; 59922</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>106747</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137713</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>244460</t>
+          <t>262611</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46664; 78788</t>
+          <t>46153; 78317</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>78454; 133443</t>
+          <t>88465; 139871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109008; 158748</t>
+          <t>106420; 155675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113616; 163538</t>
+          <t>129794; 175096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>164809; 223213</t>
+          <t>165408; 221190</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>205046; 281502</t>
+          <t>234051; 298543</t>
         </is>
       </c>
     </row>
